--- a/data/trans_orig/P19C07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21006</t>
+          <t>20921</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9060</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>24884</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>365296</t>
+          <t>365381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>380245</t>
+          <t>379940</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>258609</t>
+          <t>259323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267306</t>
+          <t>267321</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>629215</t>
+          <t>629706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>645530</t>
+          <t>645909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5646</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>17668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24169</t>
+          <t>24118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17385</t>
+          <t>18039</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37598</t>
+          <t>37500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>281398</t>
+          <t>282537</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>294559</t>
+          <t>295311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309396</t>
+          <t>309447</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>324033</t>
+          <t>323880</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>596172</t>
+          <t>596270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>616385</t>
+          <t>615731</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27292</t>
+          <t>26916</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>952</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>13427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>31661</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>402975</t>
+          <t>403351</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>418913</t>
+          <t>419160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>132054</t>
+          <t>130840</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139125</t>
+          <t>139116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>538503</t>
+          <t>538674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>556997</t>
+          <t>556908</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>17211</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>37812</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32226</t>
+          <t>33589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35122</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63563</t>
+          <t>63750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>834660</t>
+          <t>833642</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>854966</t>
+          <t>854243</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>564023</t>
+          <t>562660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>581942</t>
+          <t>582352</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1404139</t>
+          <t>1403952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1432580</t>
+          <t>1432123</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,58%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32265</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>19734</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42253</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>232388</t>
+          <t>231488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243968</t>
+          <t>243283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>423815</t>
+          <t>425113</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>443646</t>
+          <t>443687</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>661754</t>
+          <t>662394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>684308</t>
+          <t>684273</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>21614</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>42180</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29267</t>
+          <t>30263</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53384</t>
+          <t>56237</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195219</t>
+          <t>194160</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206912</t>
+          <t>206700</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>904960</t>
+          <t>903436</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>925672</t>
+          <t>924002</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1104465</t>
+          <t>1101612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1128582</t>
+          <t>1127586</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67976</t>
+          <t>67018</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>102751</t>
+          <t>104667</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>77366</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>115656</t>
+          <t>114827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156698</t>
+          <t>153510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207471</t>
+          <t>206485</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2345637</t>
+          <t>2343721</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2380412</t>
+          <t>2381370</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2624208</t>
+          <t>2625037</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2663277</t>
+          <t>2662498</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4980781</t>
+          <t>4981767</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5031554</t>
+          <t>5034742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7172</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24744</t>
+          <t>22952</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8970</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>27272</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19415</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45078</t>
+          <t>43391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>370600</t>
+          <t>372392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>388172</t>
+          <t>388480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>267863</t>
+          <t>266682</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284984</t>
+          <t>285286</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>644221</t>
+          <t>645908</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>669884</t>
+          <t>670973</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11271</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2493</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5829</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>19066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372453</t>
+          <t>372958</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381745</t>
+          <t>381803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>299857</t>
+          <t>301594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311008</t>
+          <t>311413</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678971</t>
+          <t>678159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>691358</t>
+          <t>691396</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26883</t>
+          <t>26675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>15641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34816</t>
+          <t>36115</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508605</t>
+          <t>508813</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525771</t>
+          <t>525653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226558</t>
+          <t>226488</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>237645</t>
+          <t>236811</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>741337</t>
+          <t>740038</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>761485</t>
+          <t>760512</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17286</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40866</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41444</t>
+          <t>41459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42211</t>
+          <t>41267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>73575</t>
+          <t>72289</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>931863</t>
+          <t>932253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>955443</t>
+          <t>955491</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>657483</t>
+          <t>657468</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679737</t>
+          <t>679339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1598081</t>
+          <t>1599367</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1629445</t>
+          <t>1630389</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>16779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25990</t>
+          <t>25763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16577</t>
+          <t>16693</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37624</t>
+          <t>37745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>387020</t>
+          <t>386533</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>398830</t>
+          <t>398531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>643833</t>
+          <t>644060</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>660401</t>
+          <t>660318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1035511</t>
+          <t>1035390</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1056558</t>
+          <t>1056442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,44%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16490</t>
+          <t>17391</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35501</t>
+          <t>35535</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27820</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52139</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51365</t>
+          <t>51351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>84111</t>
+          <t>83227</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185702</t>
+          <t>185668</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>204713</t>
+          <t>203812</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>873246</t>
+          <t>872264</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>897565</t>
+          <t>896928</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1062477</t>
+          <t>1063361</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1095223</t>
+          <t>1095237</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>79827</t>
+          <t>78798</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>119066</t>
+          <t>117446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>91727</t>
+          <t>93006</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>137779</t>
+          <t>136126</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>180710</t>
+          <t>180396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241025</t>
+          <t>238162</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2792734</t>
+          <t>2794354</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2831973</t>
+          <t>2833002</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3004478</t>
+          <t>3006131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3050530</t>
+          <t>3049251</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5813032</t>
+          <t>5815895</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5873347</t>
+          <t>5873661</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1996</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18575</t>
+          <t>19918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25197</t>
+          <t>26431</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>375926</t>
+          <t>374900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>385655</t>
+          <t>385618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>297241</t>
+          <t>295898</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>311198</t>
+          <t>310760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>678233</t>
+          <t>676999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>694328</t>
+          <t>694284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19302</t>
+          <t>18721</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5291</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12888</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32439</t>
+          <t>30778</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297356</t>
+          <t>297937</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311642</t>
+          <t>311759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>315108</t>
+          <t>314326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328284</t>
+          <t>328243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617793</t>
+          <t>619454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>637162</t>
+          <t>637344</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22927</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1080</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>11898</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>10577</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>28765</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>382284</t>
+          <t>382252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>397567</t>
+          <t>397841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127349</t>
+          <t>127523</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138306</t>
+          <t>138341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>516602</t>
+          <t>515868</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>534508</t>
+          <t>534056</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,06%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33087</t>
+          <t>32636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20648</t>
+          <t>20656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41271</t>
+          <t>40526</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39146</t>
+          <t>40684</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>69124</t>
+          <t>68474</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>846418</t>
+          <t>846869</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>865367</t>
+          <t>866150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642760</t>
+          <t>643505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>663383</t>
+          <t>663375</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1494412</t>
+          <t>1495062</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1524390</t>
+          <t>1522852</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16763</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>24748</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34417</t>
+          <t>34716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>408406</t>
+          <t>408480</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421200</t>
+          <t>420864</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>534869</t>
+          <t>532733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>549411</t>
+          <t>548748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>948233</t>
+          <t>947934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>967286</t>
+          <t>967015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25002</t>
+          <t>24870</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23206</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45771</t>
+          <t>45330</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36186</t>
+          <t>36658</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62095</t>
+          <t>62206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216546</t>
+          <t>216678</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233025</t>
+          <t>232438</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>779518</t>
+          <t>779959</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>802083</t>
+          <t>801793</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1004742</t>
+          <t>1004631</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1030651</t>
+          <t>1030179</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>58757</t>
+          <t>59678</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>93809</t>
+          <t>95215</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85256</t>
+          <t>83575</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125249</t>
+          <t>123236</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153324</t>
+          <t>155413</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>209323</t>
+          <t>206753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2561896</t>
+          <t>2560490</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2596948</t>
+          <t>2596027</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2730364</t>
+          <t>2732377</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2770357</t>
+          <t>2772038</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5301995</t>
+          <t>5304565</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5357994</t>
+          <t>5355905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por ortodoncia en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>12468</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29862</t>
+          <t>28920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17912</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37550</t>
+          <t>38151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>34618</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60995</t>
+          <t>59270</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>468620</t>
+          <t>469562</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486769</t>
+          <t>486014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>403375</t>
+          <t>402774</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423013</t>
+          <t>423221</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>878412</t>
+          <t>880137</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>905930</t>
+          <t>904789</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23318</t>
+          <t>23930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10584</t>
+          <t>10518</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26437</t>
+          <t>25024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>21529</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42293</t>
+          <t>43772</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>425100</t>
+          <t>424488</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>440820</t>
+          <t>441160</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>351169</t>
+          <t>352582</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367022</t>
+          <t>367088</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>783730</t>
+          <t>782251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>804869</t>
+          <t>804494</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29228</t>
+          <t>28594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9900</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34394</t>
+          <t>35103</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631501</t>
+          <t>632135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656407</t>
+          <t>656584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155068</t>
+          <t>155089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162535</t>
+          <t>162413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>791303</t>
+          <t>790594</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>818540</t>
+          <t>818181</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16868</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39420</t>
+          <t>40730</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19997</t>
+          <t>18686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54792</t>
+          <t>54542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44946</t>
+          <t>45055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84590</t>
+          <t>86936</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9757,7 +9757,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>958731</t>
+          <t>957421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>981283</t>
+          <t>979909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>904077</t>
+          <t>904327</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>938872</t>
+          <t>940183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1872430</t>
+          <t>1870084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1912074</t>
+          <t>1911965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7457</t>
+          <t>6874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40331</t>
+          <t>44512</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15330</t>
+          <t>15073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32279</t>
+          <t>32762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>26875</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61861</t>
+          <t>62706</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>398521</t>
+          <t>394340</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>431395</t>
+          <t>431978</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>781702</t>
+          <t>781219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>798651</t>
+          <t>798908</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1190972</t>
+          <t>1190127</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1227256</t>
+          <t>1225958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29130</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15760</t>
+          <t>15890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41106</t>
+          <t>42169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>23370</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57906</t>
+          <t>58484</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204082</t>
+          <t>202444</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230198</t>
+          <t>230068</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>702804</t>
+          <t>701741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>728150</t>
+          <t>728020</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>919216</t>
+          <t>918638</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>954368</t>
+          <t>953752</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>74973</t>
+          <t>75478</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132312</t>
+          <t>133840</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108318</t>
+          <t>105360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160686</t>
+          <t>159643</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>197837</t>
+          <t>194450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>281759</t>
+          <t>276606</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3145531</t>
+          <t>3144003</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3202870</t>
+          <t>3202365</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3339573</t>
+          <t>3340616</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3391941</t>
+          <t>3394899</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6496343</t>
+          <t>6501496</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6580265</t>
+          <t>6583652</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P19C07-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20921</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8964</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24884</t>
+          <t>24700</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>365381</t>
+          <t>365761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>379940</t>
+          <t>380206</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259323</t>
+          <t>259514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>267321</t>
+          <t>267322</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>629706</t>
+          <t>629890</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>645909</t>
+          <t>645546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4894</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24118</t>
+          <t>24033</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18039</t>
+          <t>17448</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37500</t>
+          <t>37136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282537</t>
+          <t>281207</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>295311</t>
+          <t>294964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>309447</t>
+          <t>309532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>323880</t>
+          <t>324628</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>596270</t>
+          <t>596634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>615731</t>
+          <t>616322</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11107</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26916</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>956</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31661</t>
+          <t>30418</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>403351</t>
+          <t>403127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>419160</t>
+          <t>419540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130840</t>
+          <t>131467</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>139116</t>
+          <t>139112</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>538674</t>
+          <t>539917</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>556908</t>
+          <t>557381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>16491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37812</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>13966</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33589</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63750</t>
+          <t>63485</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833642</t>
+          <t>834680</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>854243</t>
+          <t>854963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>562660</t>
+          <t>562648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>582352</t>
+          <t>582283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1403952</t>
+          <t>1404217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1432123</t>
+          <t>1431775</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>15901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>12638</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30967</t>
+          <t>30780</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,47 +2155,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>29002</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>19158</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>41367</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>2,72%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>6,79%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>29002</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>19734</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>41613</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>231488</t>
+          <t>232026</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>243283</t>
+          <t>243957</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>425113</t>
+          <t>425300</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>443687</t>
+          <t>443442</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +2268,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>675005</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>662640</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>684849</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>94,12%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>97,28%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>675005</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>662394</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>684273</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5416</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18073</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21320</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30263</t>
+          <t>29032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56237</t>
+          <t>52738</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194160</t>
+          <t>194850</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>206700</t>
+          <t>206817</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>903436</t>
+          <t>902705</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>924002</t>
+          <t>924296</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1101612</t>
+          <t>1105111</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1127586</t>
+          <t>1128817</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67018</t>
+          <t>67657</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104667</t>
+          <t>104336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77366</t>
+          <t>75897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114827</t>
+          <t>114746</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153510</t>
+          <t>155812</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206485</t>
+          <t>204843</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2343721</t>
+          <t>2344052</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2381370</t>
+          <t>2380731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2625037</t>
+          <t>2625118</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2662498</t>
+          <t>2663967</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4981767</t>
+          <t>4983409</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5034742</t>
+          <t>5032440</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6864</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22952</t>
+          <t>24030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>8968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27272</t>
+          <t>27300</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18326</t>
+          <t>18555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43391</t>
+          <t>42158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372392</t>
+          <t>371314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>388480</t>
+          <t>388516</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>266682</t>
+          <t>266654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285286</t>
+          <t>284986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>645908</t>
+          <t>647141</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>670973</t>
+          <t>670744</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>11975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>19165</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>372958</t>
+          <t>372713</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>381803</t>
+          <t>381782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>301594</t>
+          <t>301526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>311413</t>
+          <t>311426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>678159</t>
+          <t>678060</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>691396</t>
+          <t>691245</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26675</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15641</t>
+          <t>15698</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36115</t>
+          <t>34773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>508813</t>
+          <t>508109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>525653</t>
+          <t>526101</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>226488</t>
+          <t>227143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>236811</t>
+          <t>237697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>740038</t>
+          <t>741380</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>760512</t>
+          <t>760455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17238</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40476</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19588</t>
+          <t>19737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41459</t>
+          <t>41712</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41267</t>
+          <t>41261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>72289</t>
+          <t>72000</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>932253</t>
+          <t>931821</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>955491</t>
+          <t>955371</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>657468</t>
+          <t>657215</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>679339</t>
+          <t>679190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1599367</t>
+          <t>1599656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1630389</t>
+          <t>1630395</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4103</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16779</t>
+          <t>16108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25763</t>
+          <t>26814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16693</t>
+          <t>16437</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37745</t>
+          <t>37096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386533</t>
+          <t>387204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>398531</t>
+          <t>399209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>644060</t>
+          <t>643009</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>660318</t>
+          <t>660143</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1035390</t>
+          <t>1036039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1056442</t>
+          <t>1056698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35535</t>
+          <t>37297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28457</t>
+          <t>28899</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53121</t>
+          <t>53640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>50757</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83227</t>
+          <t>82615</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185668</t>
+          <t>183906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203812</t>
+          <t>203058</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>872264</t>
+          <t>871745</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>896928</t>
+          <t>896486</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1063361</t>
+          <t>1063973</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1095237</t>
+          <t>1095831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>78798</t>
+          <t>76165</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>117446</t>
+          <t>118646</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93006</t>
+          <t>93676</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136126</t>
+          <t>137436</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>180396</t>
+          <t>179516</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>238162</t>
+          <t>236834</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2794354</t>
+          <t>2793154</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2833002</t>
+          <t>2835635</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3006131</t>
+          <t>3004821</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3049251</t>
+          <t>3048581</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5815895</t>
+          <t>5817223</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5873661</t>
+          <t>5874541</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,03%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12714</t>
+          <t>12004</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19918</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9146</t>
+          <t>9186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26431</t>
+          <t>26748</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374900</t>
+          <t>375610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>385618</t>
+          <t>385651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>295898</t>
+          <t>296487</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>310760</t>
+          <t>310864</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>676999</t>
+          <t>676682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>694284</t>
+          <t>694244</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>13080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30778</t>
+          <t>31750</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297937</t>
+          <t>297273</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>311759</t>
+          <t>311053</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>314326</t>
+          <t>316211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328243</t>
+          <t>328358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>619454</t>
+          <t>618482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>637344</t>
+          <t>637152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>22579</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>28833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>382252</t>
+          <t>382632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>397841</t>
+          <t>397405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127523</t>
+          <t>128035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138341</t>
+          <t>138355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>515868</t>
+          <t>515800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>534056</t>
+          <t>533398</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32636</t>
+          <t>33120</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20656</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40526</t>
+          <t>42078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>40684</t>
+          <t>38821</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68474</t>
+          <t>64961</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>846869</t>
+          <t>846385</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>866150</t>
+          <t>865330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>643505</t>
+          <t>641953</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>663375</t>
+          <t>663090</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1495062</t>
+          <t>1498575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1522852</t>
+          <t>1524715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16689</t>
+          <t>17234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24748</t>
+          <t>24610</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34716</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>408480</t>
+          <t>407935</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>420864</t>
+          <t>421102</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>532733</t>
+          <t>532871</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>548748</t>
+          <t>548857</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>947934</t>
+          <t>947281</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>967015</t>
+          <t>967852</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24870</t>
+          <t>24679</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>23668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45330</t>
+          <t>44541</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36658</t>
+          <t>36188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62206</t>
+          <t>63252</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216678</t>
+          <t>216869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232438</t>
+          <t>232484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>779959</t>
+          <t>780748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>801793</t>
+          <t>801621</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1004631</t>
+          <t>1003585</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1030179</t>
+          <t>1030649</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59678</t>
+          <t>59910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95215</t>
+          <t>94019</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83575</t>
+          <t>85092</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123236</t>
+          <t>124134</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>155413</t>
+          <t>155312</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206753</t>
+          <t>206020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2560490</t>
+          <t>2561686</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2596027</t>
+          <t>2595795</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2732377</t>
+          <t>2731479</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2772038</t>
+          <t>2770521</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5304565</t>
+          <t>5305298</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5355905</t>
+          <t>5356006</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19149</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>31496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26582</t>
+          <t>27131</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17704</t>
+          <t>19399</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38151</t>
+          <t>38196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>45730</t>
+          <t>48498</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34618</t>
+          <t>35838</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59270</t>
+          <t>63827</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>479333</t>
+          <t>519896</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>469562</t>
+          <t>509767</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486014</t>
+          <t>527269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>414343</t>
+          <t>454196</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>402774</t>
+          <t>443131</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423221</t>
+          <t>461928</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>893677</t>
+          <t>974092</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>880137</t>
+          <t>958763</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>904789</t>
+          <t>986752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>498482</t>
+          <t>541263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440925</t>
+          <t>481327</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>939407</t>
+          <t>1022590</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>25155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16683</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25024</t>
+          <t>27290</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>31525</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21529</t>
+          <t>21781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43772</t>
+          <t>44591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>434515</t>
+          <t>465194</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424488</t>
+          <t>454177</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>441160</t>
+          <t>471611</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>360923</t>
+          <t>400533</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>352582</t>
+          <t>390630</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>367088</t>
+          <t>407256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>795437</t>
+          <t>865728</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>782251</t>
+          <t>852662</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>804494</t>
+          <t>875472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>448418</t>
+          <t>479332</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>377606</t>
+          <t>417920</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>826023</t>
+          <t>897253</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>17882</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>10264</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28594</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>20108</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35103</t>
+          <t>36304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>645783</t>
+          <t>445983</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>632135</t>
+          <t>432887</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656584</t>
+          <t>453601</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>159806</t>
+          <t>178874</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155089</t>
+          <t>174036</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162413</t>
+          <t>182110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>805589</t>
+          <t>624856</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>790594</t>
+          <t>612394</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>818181</t>
+          <t>633504</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>660729</t>
+          <t>463865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164968</t>
+          <t>184833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>825697</t>
+          <t>648698</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>34249</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40730</t>
+          <t>51171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38100</t>
+          <t>43973</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18686</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54542</t>
+          <t>58535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>64992</t>
+          <t>78223</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45055</t>
+          <t>62333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86936</t>
+          <t>99549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>971259</t>
+          <t>1061450</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>957421</t>
+          <t>1044528</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>979909</t>
+          <t>1073828</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>920769</t>
+          <t>792817</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>904327</t>
+          <t>778255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>940183</t>
+          <t>804145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1892028</t>
+          <t>1854266</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1870084</t>
+          <t>1832940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1911965</t>
+          <t>1870156</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>96,77%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>998151</t>
+          <t>1095699</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>958869</t>
+          <t>836790</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1957020</t>
+          <t>1932489</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>16616</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44512</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>24283</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32762</t>
+          <t>33891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39007</t>
+          <t>39122</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26875</t>
+          <t>27042</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>57684</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>422236</t>
+          <t>495009</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>394340</t>
+          <t>475723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>431978</t>
+          <t>502961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>791590</t>
+          <t>769222</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>781219</t>
+          <t>759614</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>798908</t>
+          <t>775991</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1213826</t>
+          <t>1264231</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1190127</t>
+          <t>1245669</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1225958</t>
+          <t>1276311</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>438852</t>
+          <t>509848</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>813981</t>
+          <t>793505</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1252833</t>
+          <t>1303353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3718</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>26607</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>25252</t>
+          <t>28938</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42169</t>
+          <t>44906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>36790</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>25420</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58484</t>
+          <t>56791</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,44%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>221674</t>
+          <t>215414</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>202444</t>
+          <t>199180</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230068</t>
+          <t>222069</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>718658</t>
+          <t>789804</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>701741</t>
+          <t>773836</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>728020</t>
+          <t>800080</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>940332</t>
+          <t>1005218</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>918638</t>
+          <t>987738</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>953752</t>
+          <t>1019109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>233212</t>
+          <t>225787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>743910</t>
+          <t>818742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>977122</t>
+          <t>1044529</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>103043</t>
+          <t>112849</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75478</t>
+          <t>91723</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>133840</t>
+          <t>140413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>134170</t>
+          <t>147671</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105360</t>
+          <t>126126</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159643</t>
+          <t>175476</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>237213</t>
+          <t>260520</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>194450</t>
+          <t>226719</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>276606</t>
+          <t>295335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3174800</t>
+          <t>3202946</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3144003</t>
+          <t>3175382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3202365</t>
+          <t>3224072</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3366089</t>
+          <t>3385447</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3340616</t>
+          <t>3357642</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3394899</t>
+          <t>3406992</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6540889</t>
+          <t>6588393</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6501496</t>
+          <t>6553578</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6583652</t>
+          <t>6622194</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3277843</t>
+          <t>3315795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3500259</t>
+          <t>3533118</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6778102</t>
+          <t>6848913</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
